--- a/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
+++ b/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
@@ -938,11 +938,11 @@
         </is>
       </c>
       <c r="B18" s="63" t="n">
-        <v>0.029</v>
+        <v>0.035</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Card and mobile wallet fees on total sales. A city food truck takes cards or contactless on most tickets. The example (2.9%) is roughly 2.6% plus 0.15 per sale, a typical card reader rate, averaged over the check (kit estimate).</t>
+          <t>Card and mobile wallet fees on total sales. A city food truck takes cards or contactless on most tickets. The example (3.5%) is a blended rate: a percentage plus a per-transaction fee, which weighs more on small tickets. Check your processor's statement and enter your effective rate (kit estimate).</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pay periods per year</t>
+          <t>Monthly pay periods per year (keep 12)</t>
         </is>
       </c>
       <c r="B21" s="18" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Annual gross pay = monthly gross pay × pay periods</t>
+          <t>Annual gross pay = monthly gross pay × this number. Keep 12 in the US: it counts the monthly salaries the model pays in a year, not how often you run payroll (weekly or biweekly payroll pays the same annual amount)</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Principal requested. The Financing tab checks that the sources of funds match the total cash needed on the Startup Costs tab (which includes working capital and the startup contingency). Copy the loan suggested there into this cell until the difference reaches zero.</t>
+          <t>Principal requested — bank or SBA 7(a): if your loan is an SBA 7(a), this is the cell. It is the only loan that the amortization schedule, the P&amp;L interest and the DSCR use. The Financing tab checks that the sources of funds match the total cash needed on the Startup Costs tab (which includes working capital and the startup contingency): copy the loan suggested there into this cell until the difference reaches zero.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A new food truck does not sell on day one what it sells in month six: you have to test locations, get into markets and let people find you. At 100% the ramp disappears and year 1 runs at steady state.</t>
+          <t>A new food truck does not sell on day one what it sells in month six: you have to test locations, get into markets and let people find you. Customers per day above are the year-1 AVERAGE: the ramp only spreads year 1's sales across the months (slower start, stronger finish) and keeps the annual total. At 100% there is no ramp.</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>At the window you get paid on the spot (0 days). Raise it if you work with event organizers or catering clients who pay at 15 or 30 days, or with platforms that settle later.</t>
+          <t>At 1 day, card settlements reach your bank the next business day. Raise it if you work with event organizers or catering clients who pay at 15 or 30 days, or with platforms that settle later.</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid count" error="Pay periods per year, from 12 to 16. The model pays 12 monthly installments; extra pay periods apply only if you enter more than 12." type="whole" operator="between">
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid count" error="Monthly pay periods per year, from 12 to 16. Keep 12 in the US: it is not your payroll frequency. Extra pay periods apply only if you enter more than 12." type="whole" operator="between">
       <formula1>12</formula1>
       <formula2>16</formula2>
     </dataValidation>
@@ -2708,19 +2708,19 @@
       </c>
       <c r="B17" s="40">
         <f>IFERROR(IF(B9="","",B9*'0. Assumptions'!$B$18),"")</f>
-        <v>8444.800000000001</v>
+        <v>10192.000000000002</v>
       </c>
       <c r="C17" s="40">
         <f>IFERROR(IF(C9="","",C9*'0. Assumptions'!$B$18),"")</f>
-        <v>9711.52</v>
+        <v>11720.800000000001</v>
       </c>
       <c r="D17" s="40">
         <f>IFERROR(IF(D9="","",D9*'0. Assumptions'!$B$18),"")</f>
-        <v>10682.672</v>
+        <v>12892.880000000001</v>
       </c>
       <c r="E17" s="68">
         <f>IFERROR(B17/$B$9,"")</f>
-        <v>0.029000000000000005</v>
+        <v>0.035</v>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
@@ -2772,19 +2772,19 @@
       </c>
       <c r="B19" s="66">
         <f>IFERROR(IF(B9="","",SUM(B13:B18)),"")</f>
-        <v>119856.46399999999</v>
+        <v>121603.664</v>
       </c>
       <c r="C19" s="66">
         <f>IFERROR(IF(C9="","",SUM(C13:C18)),"")</f>
-        <v>137834.9336</v>
+        <v>139844.21360000002</v>
       </c>
       <c r="D19" s="66">
         <f>IFERROR(IF(D9="","",SUM(D13:D18)),"")</f>
-        <v>151618.42695999998</v>
+        <v>153828.63496</v>
       </c>
       <c r="E19" s="67">
         <f>IFERROR(B19/$B$9,"")</f>
-        <v>0.411595</v>
+        <v>0.417595</v>
       </c>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
@@ -2798,19 +2798,19 @@
       </c>
       <c r="B20" s="66">
         <f>IFERROR(IF(B9="","",B9-B19),"")</f>
-        <v>171343.53600000002</v>
+        <v>169596.336</v>
       </c>
       <c r="C20" s="66">
         <f>IFERROR(IF(C9="","",C9-C19),"")</f>
-        <v>197045.0664</v>
+        <v>195035.78639999998</v>
       </c>
       <c r="D20" s="66">
         <f>IFERROR(IF(D9="","",D9-D19),"")</f>
-        <v>216749.57304000002</v>
+        <v>214539.36504</v>
       </c>
       <c r="E20" s="67">
         <f>IFERROR(B20/$B$9,"")</f>
-        <v>0.5884050000000001</v>
+        <v>0.5824050000000001</v>
       </c>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
@@ -3394,19 +3394,19 @@
       </c>
       <c r="B41" s="52">
         <f>IFERROR(IF(B9="","",B20-B38),"")</f>
-        <v>27695.307428571454</v>
+        <v>25948.107428571442</v>
       </c>
       <c r="C41" s="52">
         <f>IFERROR(IF(C9="","",C20-C38),"")</f>
-        <v>48577.379425218096</v>
+        <v>46568.09942521807</v>
       </c>
       <c r="D41" s="52">
         <f>IFERROR(IF(D9="","",D20-D38),"")</f>
-        <v>63580.48182152945</v>
+        <v>61370.27382152944</v>
       </c>
       <c r="E41" s="69">
         <f>IFERROR(B41/$B$9,"")</f>
-        <v>0.09510751177394043</v>
+        <v>0.0891075117739404</v>
       </c>
     </row>
     <row r="42">
@@ -3441,15 +3441,15 @@
       </c>
       <c r="B43" s="42">
         <f>IFERROR(IF(B9="","",MAX(0,B41-B42)),"")</f>
-        <v>27695.307428571454</v>
+        <v>25948.107428571442</v>
       </c>
       <c r="C43" s="42">
         <f>IFERROR(IF(C9="","",MAX(0,C41-C42)),"")</f>
-        <v>48577.379425218096</v>
+        <v>46568.09942521807</v>
       </c>
       <c r="D43" s="42">
         <f>IFERROR(IF(D9="","",MAX(0,D41-D42)),"")</f>
-        <v>63580.48182152945</v>
+        <v>61370.27382152944</v>
       </c>
     </row>
     <row r="44">
@@ -3503,15 +3503,15 @@
       </c>
       <c r="B46" s="42">
         <f>IFERROR(IF(B9="","",IF(B45="",0,B43*B45)),"")</f>
-        <v>6923.826857142863</v>
+        <v>6487.0268571428605</v>
       </c>
       <c r="C46" s="42">
         <f>IFERROR(IF(C9="","",IF(C45="",0,C43*C45)),"")</f>
-        <v>12144.344856304524</v>
+        <v>11642.024856304517</v>
       </c>
       <c r="D46" s="42">
         <f>IFERROR(IF(D9="","",IF(D45="",0,D43*D45)),"")</f>
-        <v>15895.120455382363</v>
+        <v>15342.56845538236</v>
       </c>
     </row>
     <row r="47">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="B48" s="52">
         <f>IFERROR(IF(B9="","",B41-B46),"")</f>
-        <v>20771.48057142859</v>
+        <v>19461.08057142858</v>
       </c>
       <c r="C48" s="52">
         <f>IFERROR(IF(C9="","",C41-C46),"")</f>
-        <v>36433.03456891357</v>
+        <v>34926.07456891355</v>
       </c>
       <c r="D48" s="52">
         <f>IFERROR(IF(D9="","",D41-D46),"")</f>
-        <v>47685.36136614709</v>
+        <v>46027.70536614708</v>
       </c>
       <c r="E48" s="69">
         <f>IFERROR(B48/$B$9,"")</f>
-        <v>0.07133063383045532</v>
+        <v>0.06683063383045529</v>
       </c>
     </row>
     <row r="49">
@@ -3603,15 +3603,15 @@
       </c>
       <c r="B51" s="65">
         <f>IFERROR(IF(B9="","",B20/B9),"")</f>
-        <v>0.5884050000000001</v>
+        <v>0.5824050000000001</v>
       </c>
       <c r="C51" s="65">
         <f>IFERROR(IF(C9="","",C20/C9),"")</f>
-        <v>0.5884050000000001</v>
+        <v>0.582405</v>
       </c>
       <c r="D51" s="65">
         <f>IFERROR(IF(D9="","",D20/D9),"")</f>
-        <v>0.5884050000000001</v>
+        <v>0.5824050000000001</v>
       </c>
       <c r="E51" s="70" t="n">
         <v>0.58</v>
@@ -3730,15 +3730,15 @@
       </c>
       <c r="B56" s="65">
         <f>IFERROR(IF(B9="","",B48/B9),"")</f>
-        <v>0.07133063383045532</v>
+        <v>0.06683063383045529</v>
       </c>
       <c r="C56" s="65">
         <f>IFERROR(IF(C9="","",C48/C9),"")</f>
-        <v>0.10879429816326318</v>
+        <v>0.10429429816326312</v>
       </c>
       <c r="D56" s="65">
         <f>IFERROR(IF(D9="","",D48/D9),"")</f>
-        <v>0.1294503359850668</v>
+        <v>0.12495033598506677</v>
       </c>
       <c r="E56" s="70" t="n">
         <v>0.06</v>
@@ -4025,15 +4025,15 @@
       </c>
       <c r="B9" s="61">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",'3-Year P&amp;L'!$B$19/('3-Year P&amp;L'!$B$6*'3-Year P&amp;L'!$B$8)),"")</f>
-        <v>5.7623299999999995</v>
+        <v>5.84633</v>
       </c>
       <c r="C9" s="61">
         <f>IFERROR(IF('3-Year P&amp;L'!$C$9="","",'3-Year P&amp;L'!$C$19/('3-Year P&amp;L'!$C$6*'3-Year P&amp;L'!$C$8)),"")</f>
-        <v>5.7623299999999995</v>
+        <v>5.846330000000001</v>
       </c>
       <c r="D9" s="61">
         <f>IFERROR(IF('3-Year P&amp;L'!$D$9="","",'3-Year P&amp;L'!$D$19/('3-Year P&amp;L'!$D$6*'3-Year P&amp;L'!$D$8)),"")</f>
-        <v>5.7623299999999995</v>
+        <v>5.84633</v>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
@@ -4050,15 +4050,15 @@
       </c>
       <c r="B10" s="61">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",B8-B9),"")</f>
-        <v>8.237670000000001</v>
+        <v>8.15367</v>
       </c>
       <c r="C10" s="61">
         <f>IFERROR(IF('3-Year P&amp;L'!$C$9="","",C8-C9),"")</f>
-        <v>8.237670000000001</v>
+        <v>8.153669999999998</v>
       </c>
       <c r="D10" s="61">
         <f>IFERROR(IF('3-Year P&amp;L'!$D$9="","",D8-D9),"")</f>
-        <v>8.237670000000001</v>
+        <v>8.15367</v>
       </c>
       <c r="E10" s="28" t="inlineStr">
         <is>
@@ -4137,15 +4137,15 @@
       </c>
       <c r="B14" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",IF(B10&lt;=0,"",B6/B10)),"")</f>
-        <v>17437.968329810315</v>
+        <v>17617.616186506024</v>
       </c>
       <c r="C14" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$C$9="","",IF(C10&lt;=0,"",C6/C10)),"")</f>
-        <v>18023.01949152878</v>
+        <v>18208.694609271894</v>
       </c>
       <c r="D14" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$D$9="","",IF(D10&lt;=0,"",D6/D10)),"")</f>
-        <v>18593.739639785344</v>
+        <v>18785.294378907973</v>
       </c>
       <c r="E14" s="28" t="n"/>
       <c r="F14" s="28" t="n"/>
@@ -4158,15 +4158,15 @@
       </c>
       <c r="B15" s="44">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",B14/B11),"")</f>
-        <v>67.0691089608089</v>
+        <v>67.7600622557924</v>
       </c>
       <c r="C15" s="44">
         <f>IFERROR(IF('3-Year P&amp;L'!$C$9="","",C14/C11),"")</f>
-        <v>69.31930573664916</v>
+        <v>70.0334408048919</v>
       </c>
       <c r="D15" s="44">
         <f>IFERROR(IF('3-Year P&amp;L'!$D$9="","",D14/D11),"")</f>
-        <v>71.51438322994363</v>
+        <v>72.25113222656913</v>
       </c>
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
@@ -4179,15 +4179,15 @@
       </c>
       <c r="B16" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",B14*B8),"")</f>
-        <v>244131.5566173444</v>
+        <v>246646.62661108433</v>
       </c>
       <c r="C16" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$C$9="","",C14*C8),"")</f>
-        <v>252322.27288140293</v>
+        <v>254921.72452980652</v>
       </c>
       <c r="D16" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$D$9="","",D14*D8),"")</f>
-        <v>260312.35495699482</v>
+        <v>262994.1213047116</v>
       </c>
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
@@ -4237,15 +4237,15 @@
       </c>
       <c r="B19" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",IF(B10&lt;=0,"",B18/B10)),"")</f>
-        <v>17107.04798401328</v>
+        <v>17283.286663118168</v>
       </c>
       <c r="C19" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$C$9="","",IF(C10&lt;=0,"",C18/C10)),"")</f>
-        <v>17835.409280350716</v>
+        <v>18019.1516171818</v>
       </c>
       <c r="D19" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$D$9="","",IF(D10&lt;=0,"",D18/D10)),"")</f>
-        <v>18563.770576688148</v>
+        <v>18755.016571245425</v>
       </c>
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
@@ -4258,15 +4258,15 @@
       </c>
       <c r="B20" s="45">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",B19/B11),"")</f>
-        <v>65.79633840005107</v>
+        <v>66.47417947353142</v>
       </c>
       <c r="C20" s="45">
         <f>IFERROR(IF('3-Year P&amp;L'!$C$9="","",C19/C11),"")</f>
-        <v>68.59772800134891</v>
+        <v>69.30442929685307</v>
       </c>
       <c r="D20" s="45">
         <f>IFERROR(IF('3-Year P&amp;L'!$D$9="","",D19/D11),"")</f>
-        <v>71.39911760264673</v>
+        <v>72.13467912017471</v>
       </c>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
@@ -4279,15 +4279,15 @@
       </c>
       <c r="B21" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",B19*B8),"")</f>
-        <v>239498.67177618592</v>
+        <v>241966.01328365435</v>
       </c>
       <c r="C21" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$C$9="","",C19*C8),"")</f>
-        <v>249695.72992491</v>
+        <v>252268.1226405452</v>
       </c>
       <c r="D21" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$D$9="","",D19*D8),"")</f>
-        <v>259892.7880736341</v>
+        <v>262570.23199743597</v>
       </c>
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
@@ -4333,15 +4333,15 @@
       </c>
       <c r="B24" s="68">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",B23/B20-1),"")</f>
-        <v>0.21587313132212094</v>
+        <v>0.20347480230055748</v>
       </c>
       <c r="C24" s="68">
         <f>IFERROR(IF('3-Year P&amp;L'!$C$9="","",C23/C20-1),"")</f>
-        <v>0.34115229003198033</v>
+        <v>0.32747648214422953</v>
       </c>
       <c r="D24" s="68">
         <f>IFERROR(IF('3-Year P&amp;L'!$D$9="","",D23/D20-1),"")</f>
-        <v>0.41738446353360215</v>
+        <v>0.40293131173985186</v>
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
     <row r="26" ht="46" customHeight="1">
       <c r="A26" s="28" t="str">
         <f>IFERROR("With the average check excl. sales tax above, you need "&amp;TEXT(ROUNDUP(B15,0),"0")&amp;" customers a day over your "&amp;TEXT(B11,"0")&amp;" opening days to avoid losing money (accounting break-even, depreciation included), and "&amp;TEXT(ROUNDUP(B20,0),"0")&amp;" for cash to hold (cash break-even: depreciation out, because it is not paid, and the year's loan payment in"&amp;IF(B12=0,"; no principal is repaid this year (interest-only period or no loan)","")&amp;"). The ""Revenue needed per year"" rows show the same figures in your currency.","")</f>
-        <v>With the average check excl. sales tax above, you need 68 customers a day over your 260 opening days to avoid losing money (accounting break-even, depreciation included), and 66 for cash to hold (cash break-even: depreciation out, because it is not paid, and the year's loan payment in). The "Revenue needed per year" rows show the same figures in your currency.</v>
+        <v>With the average check excl. sales tax above, you need 68 customers a day over your 260 opening days to avoid losing money (accounting break-even, depreciation included), and 67 for cash to hold (cash break-even: depreciation out, because it is not paid, and the year's loan payment in). The "Revenue needed per year" rows show the same figures in your currency.</v>
       </c>
       <c r="B26" s="28" t="n"/>
       <c r="C26" s="28" t="n"/>
@@ -4440,113 +4440,113 @@
     <row r="32">
       <c r="A32" s="61">
         <f>IFERROR($B$9*0.85,"")</f>
-        <v>4.897980499999999</v>
+        <v>4.9693805</v>
       </c>
       <c r="B32" s="44">
         <f>IFERROR(IF($B$31-$A32&lt;=0,"",$B$6/($B$31-$A32)/$B$11),"")</f>
-        <v>77.79381439507266</v>
+        <v>78.58385549284623</v>
       </c>
       <c r="C32" s="44">
         <f>IFERROR(IF($C$31-$A32&lt;=0,"",$B$6/($C$31-$A32)/$B$11),"")</f>
-        <v>60.70006626696271</v>
+        <v>61.17998735448734</v>
       </c>
       <c r="D32" s="44">
         <f>IFERROR(IF($D$31-$A32&lt;=0,"",$B$6/($D$31-$A32)/$B$11),"")</f>
-        <v>49.76510686305196</v>
+        <v>50.08723098581968</v>
       </c>
       <c r="E32" s="44">
         <f>IFERROR(IF($E$31-$A32&lt;=0,"",$B$6/($E$31-$A32)/$B$11),"")</f>
-        <v>42.168551711679775</v>
+        <v>42.39961015001526</v>
       </c>
       <c r="F32" s="28" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="61">
         <f>IFERROR($B$9*0.925,"")</f>
-        <v>5.33015525</v>
+        <v>5.40785525</v>
       </c>
       <c r="B33" s="44">
         <f>IFERROR(IF($B$31-$A33&lt;=0,"",$B$6/($B$31-$A33)/$B$11),"")</f>
-        <v>82.83448978526626</v>
+        <v>83.81083968357746</v>
       </c>
       <c r="C33" s="44">
         <f>IFERROR(IF($C$31-$A33&lt;=0,"",$B$6/($C$31-$A33)/$B$11),"")</f>
-        <v>63.72584547297538</v>
+        <v>64.30212745347275</v>
       </c>
       <c r="D33" s="44">
         <f>IFERROR(IF($D$31-$A33&lt;=0,"",$B$6/($D$31-$A33)/$B$11),"")</f>
-        <v>51.780808414591675</v>
+        <v>52.16065299836342</v>
       </c>
       <c r="E33" s="44">
         <f>IFERROR(IF($E$31-$A33&lt;=0,"",$B$6/($E$31-$A33)/$B$11),"")</f>
-        <v>43.60694213030407</v>
+        <v>43.87601935827388</v>
       </c>
       <c r="F33" s="28" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="64">
         <f>IFERROR($B$9*1.0,"")</f>
-        <v>5.7623299999999995</v>
+        <v>5.84633</v>
       </c>
       <c r="B34" s="48">
         <f>IFERROR(IF($B$31-$A34&lt;=0,"",$B$6/($B$31-$A34)/$B$11),"")</f>
-        <v>88.57364798285046</v>
+        <v>89.78271288729925</v>
       </c>
       <c r="C34" s="48">
         <f>IFERROR(IF($C$31-$A34&lt;=0,"",$B$6/($C$31-$A34)/$B$11),"")</f>
-        <v>67.0691089608089</v>
+        <v>67.7600622557924</v>
       </c>
       <c r="D34" s="48">
         <f>IFERROR(IF($D$31-$A34&lt;=0,"",$B$6/($D$31-$A34)/$B$11),"")</f>
-        <v>53.966692305298636</v>
+        <v>54.41315177794697</v>
       </c>
       <c r="E34" s="48">
         <f>IFERROR(IF($E$31-$A34&lt;=0,"",$B$6/($E$31-$A34)/$B$11),"")</f>
-        <v>45.146926401282826</v>
+        <v>45.45895904802309</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="64">
         <f>IFERROR($B$9*1.075,"")</f>
-        <v>6.194504749999999</v>
+        <v>6.28480475</v>
       </c>
       <c r="B35" s="48">
         <f>IFERROR(IF($B$31-$A35&lt;=0,"",$B$6/($B$31-$A35)/$B$11),"")</f>
-        <v>95.16727910735725</v>
+        <v>96.6709207026981</v>
       </c>
       <c r="C35" s="48">
         <f>IFERROR(IF($C$31-$A35&lt;=0,"",$B$6/($C$31-$A35)/$B$11),"")</f>
-        <v>70.78259215047075</v>
+        <v>71.61104403847547</v>
       </c>
       <c r="D35" s="48">
         <f>IFERROR(IF($D$31-$A35&lt;=0,"",$B$6/($D$31-$A35)/$B$11),"")</f>
-        <v>56.345260767240376</v>
+        <v>56.86897407575898</v>
       </c>
       <c r="E35" s="48">
         <f>IFERROR(IF($E$31-$A35&lt;=0,"",$B$6/($E$31-$A35)/$B$11),"")</f>
-        <v>46.79966194668426</v>
+        <v>47.16039084480361</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="64">
         <f>IFERROR($B$9*1.15,"")</f>
-        <v>6.626679499999999</v>
+        <v>6.723279499999999</v>
       </c>
       <c r="B36" s="48">
         <f>IFERROR(IF($B$31-$A36&lt;=0,"",$B$6/($B$31-$A36)/$B$11),"")</f>
-        <v>102.82155825493506</v>
+        <v>104.70389455215351</v>
       </c>
       <c r="C36" s="48">
         <f>IFERROR(IF($C$31-$A36&lt;=0,"",$B$6/($C$31-$A36)/$B$11),"")</f>
-        <v>74.93139445290446</v>
+        <v>75.92612452452815</v>
       </c>
       <c r="D36" s="48">
         <f>IFERROR(IF($D$31-$A36&lt;=0,"",$B$6/($D$31-$A36)/$B$11),"")</f>
-        <v>58.94316606512993</v>
+        <v>59.55695084412501</v>
       </c>
       <c r="E36" s="48">
         <f>IFERROR(IF($E$31-$A36&lt;=0,"",$B$6/($E$31-$A36)/$B$11),"")</f>
-        <v>48.578002071882764</v>
+        <v>48.994136798299365</v>
       </c>
     </row>
   </sheetData>
@@ -4807,15 +4807,15 @@
       </c>
       <c r="B13" s="40">
         <f>IFERROR(IF(B8="","",B8*'0. Assumptions'!$B$18),"")</f>
-        <v>4663.5654</v>
+        <v>5628.441000000001</v>
       </c>
       <c r="C13" s="40">
         <f>IFERROR(IF(C8="","",C8*'0. Assumptions'!$B$18),"")</f>
-        <v>8444.800000000001</v>
+        <v>10192.000000000002</v>
       </c>
       <c r="D13" s="40">
         <f>IFERROR(IF(D8="","",D8*'0. Assumptions'!$B$18),"")</f>
-        <v>14282.8712</v>
+        <v>17237.948</v>
       </c>
       <c r="E13" s="28" t="n"/>
       <c r="F13" s="28" t="n"/>
@@ -4849,15 +4849,15 @@
       </c>
       <c r="B15" s="40">
         <f>IFERROR(IF(B8="","",SUM(B9:B14)),"")</f>
-        <v>66189.66209700001</v>
+        <v>67154.537697</v>
       </c>
       <c r="C15" s="40">
         <f>IFERROR(IF(C8="","",SUM(C9:C14)),"")</f>
-        <v>119856.46399999999</v>
+        <v>121603.664</v>
       </c>
       <c r="D15" s="40">
         <f>IFERROR(IF(D8="","",SUM(D9:D14)),"")</f>
-        <v>202715.80591599995</v>
+        <v>205670.88271599996</v>
       </c>
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
@@ -4870,15 +4870,15 @@
       </c>
       <c r="B16" s="42">
         <f>IFERROR(IF(B8="","",B8-B15),"")</f>
-        <v>94622.937903</v>
+        <v>93658.062303</v>
       </c>
       <c r="C16" s="42">
         <f>IFERROR(IF(C8="","",C8-C15),"")</f>
-        <v>171343.53600000002</v>
+        <v>169596.336</v>
       </c>
       <c r="D16" s="42">
         <f>IFERROR(IF(D8="","",D8-D15),"")</f>
-        <v>289796.994084</v>
+        <v>286841.91728399997</v>
       </c>
     </row>
     <row r="17">
@@ -4913,15 +4913,15 @@
       </c>
       <c r="B18" s="52">
         <f>IFERROR(IF(B8="","",B16-B17),"")</f>
-        <v>-49025.29066842857</v>
+        <v>-49990.16626842857</v>
       </c>
       <c r="C18" s="52">
         <f>IFERROR(IF(C8="","",C16-C17),"")</f>
-        <v>27695.307428571454</v>
+        <v>25948.107428571442</v>
       </c>
       <c r="D18" s="52">
         <f>IFERROR(IF(D8="","",D16-D17),"")</f>
-        <v>146148.76551257144</v>
+        <v>143193.6887125714</v>
       </c>
     </row>
     <row r="19">
@@ -4936,11 +4936,11 @@
       </c>
       <c r="C19" s="42">
         <f>IFERROR(IF(C8="","",MAX(0,C18-'0. Assumptions'!$B$42)*'0. Assumptions'!$B$37),"")</f>
-        <v>6923.826857142863</v>
+        <v>6487.0268571428605</v>
       </c>
       <c r="D19" s="42">
         <f>IFERROR(IF(D8="","",MAX(0,D18-'0. Assumptions'!$B$42)*'0. Assumptions'!$B$37),"")</f>
-        <v>36537.19137814286</v>
+        <v>35798.42217814285</v>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
@@ -4956,15 +4956,15 @@
       </c>
       <c r="B20" s="52">
         <f>IFERROR(IF(B8="","",B18-B19),"")</f>
-        <v>-49025.29066842857</v>
+        <v>-49990.16626842857</v>
       </c>
       <c r="C20" s="52">
         <f>IFERROR(IF(C8="","",C18-C19),"")</f>
-        <v>20771.48057142859</v>
+        <v>19461.08057142858</v>
       </c>
       <c r="D20" s="52">
         <f>IFERROR(IF(D8="","",D18-D19),"")</f>
-        <v>109611.57413442858</v>
+        <v>107395.26653442855</v>
       </c>
     </row>
     <row r="21">
@@ -4975,15 +4975,15 @@
       </c>
       <c r="B21" s="48">
         <f>IFERROR(IF(B8="","",IF(B6-B15/(B5*B7)&lt;=0,"",B17/(B6-B15/(B5*B7))/B7)),"")</f>
-        <v>80.45994219805698</v>
+        <v>81.28884932143048</v>
       </c>
       <c r="C21" s="48">
         <f>IFERROR(IF(C8="","",IF(C6-C15/(C5*C7)&lt;=0,"",C17/(C6-C15/(C5*C7))/C7)),"")</f>
-        <v>67.0691089608089</v>
+        <v>67.7600622557924</v>
       </c>
       <c r="D21" s="48">
         <f>IFERROR(IF(D8="","",IF(D6-D15/(D5*D7)&lt;=0,"",D17/(D6-D15/(D5*D7))/D7)),"")</f>
-        <v>57.499542281158895</v>
+        <v>58.09190885371057</v>
       </c>
     </row>
     <row r="22">
@@ -5049,15 +5049,15 @@
       </c>
       <c r="B25" s="52">
         <f>IFERROR(IF(B8="","",'Startup Costs'!$B$25+B20+'3-Year P&amp;L'!$B$36-Financing!$B$45),"")</f>
-        <v>-14020.0780634667</v>
+        <v>-14984.9536634667</v>
       </c>
       <c r="C25" s="52">
         <f>IFERROR(IF(C8="","",'Startup Costs'!$B$25+C20+'3-Year P&amp;L'!$B$36-Financing!$B$45),"")</f>
-        <v>55776.69317639045</v>
+        <v>54466.29317639044</v>
       </c>
       <c r="D25" s="52">
         <f>IFERROR(IF(D8="","",'Startup Costs'!$B$25+D20+'3-Year P&amp;L'!$B$36-Financing!$B$45),"")</f>
-        <v>144616.78673939046</v>
+        <v>142400.47913939043</v>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C26" s="42">
         <f>IFERROR(IF(C8="","",'12-Month Cash Flow'!$M$22),"")</f>
-        <v>70692.63744662206</v>
+        <v>68985.84136244723</v>
       </c>
       <c r="E26" s="35" t="inlineStr">
         <is>
@@ -5741,10 +5741,10 @@
       <c r="D6" s="28" t="n"/>
       <c r="E6" s="28" t="n"/>
     </row>
-    <row r="7" ht="90" customHeight="1">
+    <row r="7" ht="104.75" customHeight="1">
       <c r="A7" s="46" t="inlineStr">
         <is>
-          <t>3. Only "Break-Even" is derived entirely from the rest. The other three tabs also have green cells you can edit: the pessimistic and optimistic scenarios in "Scenarios", seasonality and the launch ramp-up in "12-Month Cash Flow", and the four alternative funding sources in "Financing". Everything else is calculated.</t>
+          <t>3. Only "Break-Even" is derived entirely from the rest. The other three tabs also have green cells you can edit: the pessimistic and optimistic scenarios in "Scenarios", seasonality and the launch ramp-up in "12-Month Cash Flow", and the other funding sources in "Financing" (rows 8-11 count as sources but are not amortized: Your bank or SBA 7(a) loan goes in "Loan requested" on "0. Assumptions"). Everything else is calculated.</t>
         </is>
       </c>
       <c r="B7" s="28" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B21" s="65">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$56="","",'3-Year P&amp;L'!$B$56),"")</f>
-        <v>0.07133063383045532</v>
+        <v>0.06683063383045529</v>
       </c>
       <c r="C21" s="65">
         <f>IFERROR(IF('3-Year P&amp;L'!$E$56="","",'3-Year P&amp;L'!$E$56),"")</f>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="B22" s="65">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$51="","",'3-Year P&amp;L'!$B$51),"")</f>
-        <v>0.5884050000000001</v>
+        <v>0.5824050000000001</v>
       </c>
       <c r="C22" s="65">
         <f>IFERROR(IF('3-Year P&amp;L'!$E$51="","",'3-Year P&amp;L'!$E$51),"")</f>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="B29" s="42">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$48="","",'3-Year P&amp;L'!$B$48),"")</f>
-        <v>20771.48057142859</v>
+        <v>19461.08057142858</v>
       </c>
     </row>
     <row r="30">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="B30" s="48">
         <f>IFERROR(IF('Break-Even'!$B$15="","",'Break-Even'!$B$15),"")</f>
-        <v>67.0691089608089</v>
+        <v>67.7600622557924</v>
       </c>
     </row>
     <row r="31">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="B31">
         <f>IFERROR(IF('12-Month Cash Flow'!$B$31="","",'12-Month Cash Flow'!$B$31),"")</f>
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="33">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>It was the same expense written in two places. Now you change it in one cell and the rest of the workbook follows.</t>
+          <t>Writing it in two places counts it twice: here it lives in one cell and the rest of the workbook follows.</t>
         </is>
       </c>
     </row>
@@ -7293,55 +7293,55 @@
       </c>
       <c r="B11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*B7*(1-MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-3339.2083989825023</v>
+        <v>-3387.88549757188</v>
       </c>
       <c r="C11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(C7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+B7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-5031.425946524833</v>
+        <v>-5104.771239055474</v>
       </c>
       <c r="D11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(D7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+C7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-6762.050989881549</v>
+        <v>-6860.624359187029</v>
       </c>
       <c r="E11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(E7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+D7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-8324.04380934762</v>
+        <v>-8445.387029882579</v>
       </c>
       <c r="F11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(F7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+E7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-10123.3887936689</v>
+        <v>-10270.961851558364</v>
       </c>
       <c r="G11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(G7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+F7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-12382.611846429763</v>
+        <v>-12563.118585040724</v>
       </c>
       <c r="H11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(H7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+G7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-13642.800059610985</v>
+        <v>-13841.67711195046</v>
       </c>
       <c r="I11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(I7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+H7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-13352.43411187338</v>
+        <v>-13547.078373031167</v>
       </c>
       <c r="J11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(J7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+I7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-11984.194570261312</v>
+        <v>-12158.893406305404</v>
       </c>
       <c r="K11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(K7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+J7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-10805.132843084357</v>
+        <v>-10962.643981602818</v>
       </c>
       <c r="L11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(L7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+K7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-9951.632936098049</v>
+        <v>-10096.702233870345</v>
       </c>
       <c r="M11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",-('3-Year P&amp;L'!$B$13*(1+'3-Year P&amp;L'!$G$13)+'3-Year P&amp;L'!$B$14*(1+'3-Year P&amp;L'!$G$14)+'3-Year P&amp;L'!$B$15*(1+'3-Year P&amp;L'!$G$15)+'3-Year P&amp;L'!$B$16*(1+'3-Year P&amp;L'!$G$16)+'3-Year P&amp;L'!$B$17*(1+'3-Year P&amp;L'!$G$17)+'3-Year P&amp;L'!$B$18*(1+'3-Year P&amp;L'!$G$18))*(M7*(1-MIN(30,'0. Assumptions'!$B$59)/30)+L7*MIN(30,'0. Assumptions'!$B$59)/30)),"")</f>
-        <v>-11385.86473855957</v>
+        <v>-11551.841459441403</v>
       </c>
       <c r="N11" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(B11:M11)),"")</f>
-        <v>-117084.78904432281</v>
+        <v>-118791.58512849764</v>
       </c>
       <c r="O11" s="28" t="str">
         <f>IFERROR("Food and beverage purchases, consumables, fees and contingencies, each at ITS tax rate (column G of the P&amp;L; 0 in the US, where the sales tax you pay is part of the cost) and with the supplier payment days from ""0. Assumptions""."&amp;IF('0. Assumptions'!$B$59=0,""," With "&amp;TEXT('0. Assumptions'!$B$59,"0")&amp;" payment days, the last purchases of the year are paid next year: the ""Year"" column of this row holds "&amp;TEXT(MAX(0,12-ROUNDUP('0. Assumptions'!$B$59/30,0)),"0")&amp;" months of purchases, not the year's cost."),"")</f>
@@ -7837,55 +7837,55 @@
       </c>
       <c r="B21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(B9:B15)+IF(B20="",0,B20)),"")</f>
-        <v>-4035.141411990111</v>
+        <v>-4083.818510579489</v>
       </c>
       <c r="C21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(C9:C15)+IF(C20="",0,C20)),"")</f>
-        <v>-3110.1087321370833</v>
+        <v>-3183.4540246677243</v>
       </c>
       <c r="D21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(D9:D15)+IF(D20="",0,D20)),"")</f>
-        <v>281.443793302935</v>
+        <v>182.87042399745417</v>
       </c>
       <c r="E21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(E9:E15)+IF(E20="",0,E20)),"")</f>
-        <v>-743.2667321679091</v>
+        <v>-864.6099527028673</v>
       </c>
       <c r="F21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(F9:F15)+IF(F20="",0,F20)),"")</f>
-        <v>5699.184259769191</v>
+        <v>5551.611201879726</v>
       </c>
       <c r="G21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(G9:G15)+IF(G20="",0,G20)),"")</f>
-        <v>9606.291400487085</v>
+        <v>9425.784661876123</v>
       </c>
       <c r="H21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(H9:H15)+IF(H20="",0,H20)),"")</f>
-        <v>4645.2071108393575</v>
+        <v>4446.330058499883</v>
       </c>
       <c r="I21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(I9:I15)+IF(I20="",0,I20)),"")</f>
-        <v>9593.69562082163</v>
+        <v>9399.051359663843</v>
       </c>
       <c r="J21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(J9:J15)+IF(J20="",0,J20)),"")</f>
-        <v>6886.91165206601</v>
+        <v>6712.212816021918</v>
       </c>
       <c r="K21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(K9:K15)+IF(K20="",0,K20)),"")</f>
-        <v>-2267.167760046329</v>
+        <v>-2424.67889856479</v>
       </c>
       <c r="L21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(L9:L15)+IF(L20="",0,L20)),"")</f>
-        <v>4001.739531507927</v>
+        <v>3856.6702337356314</v>
       </c>
       <c r="M21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(M9:M15)+IF(M20="",0,M20)),"")</f>
-        <v>7854.648714169353</v>
+        <v>7688.671993287519</v>
       </c>
       <c r="N21" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",SUM(B21:M21)),"")</f>
-        <v>38413.437446622054</v>
+        <v>36706.641362447226</v>
       </c>
       <c r="O21" s="28" t="n"/>
     </row>
@@ -7897,51 +7897,51 @@
       </c>
       <c r="B22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",'Startup Costs'!$B$25+B21),"")</f>
-        <v>28244.058588009888</v>
+        <v>28195.381489420513</v>
       </c>
       <c r="C22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",B22+C21),"")</f>
-        <v>25133.949855872805</v>
+        <v>25011.92746475279</v>
       </c>
       <c r="D22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",C22+D21),"")</f>
-        <v>25415.39364917574</v>
+        <v>25194.797888750243</v>
       </c>
       <c r="E22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",D22+E21),"")</f>
-        <v>24672.12691700783</v>
+        <v>24330.187936047376</v>
       </c>
       <c r="F22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",E22+F21),"")</f>
-        <v>30371.31117677702</v>
+        <v>29881.7991379271</v>
       </c>
       <c r="G22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",F22+G21),"")</f>
-        <v>39977.60257726411</v>
+        <v>39307.58379980322</v>
       </c>
       <c r="H22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",G22+H21),"")</f>
-        <v>44622.809688103465</v>
+        <v>43753.9138583031</v>
       </c>
       <c r="I22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",H22+I21),"")</f>
-        <v>54216.505308925094</v>
+        <v>53152.96521796694</v>
       </c>
       <c r="J22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",I22+J21),"")</f>
-        <v>61103.416960991104</v>
+        <v>59865.178033988865</v>
       </c>
       <c r="K22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",J22+K21),"")</f>
-        <v>58836.249200944774</v>
+        <v>57440.49913542408</v>
       </c>
       <c r="L22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",K22+L21),"")</f>
-        <v>62837.9887324527</v>
+        <v>61297.16936915971</v>
       </c>
       <c r="M22" s="66">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",L22+M21),"")</f>
-        <v>70692.63744662206</v>
+        <v>68985.84136244723</v>
       </c>
       <c r="N22" s="28" t="n"/>
       <c r="O22" s="28" t="n"/>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="B23" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",IF(COUNT(B22:M22)=0,"",MIN(B22:M22))),"")</f>
-        <v>24672.12691700783</v>
+        <v>24330.187936047376</v>
       </c>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="B26" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",'3-Year P&amp;L'!$B$48+'3-Year P&amp;L'!$B$36+Financing!$B$44),"")</f>
-        <v>46502.90914285716</v>
+        <v>45192.509142857154</v>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="B27" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",'3-Year P&amp;L'!$C$48+'3-Year P&amp;L'!$C$36+Financing!$B$46),"")</f>
-        <v>60983.92154369548</v>
+        <v>59476.961543695455</v>
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="B28" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",'3-Year P&amp;L'!$D$48+'3-Year P&amp;L'!$D$36+Financing!$B$48),"")</f>
-        <v>70937.65258461765</v>
+        <v>69279.99658461765</v>
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B29" s="40">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",N21+Financing!$B$44+Financing!$B$45),"")</f>
-        <v>61418.85341308876</v>
+        <v>59712.05732891393</v>
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B31" s="25">
         <f>IFERROR(IF('3-Year P&amp;L'!$B$9="","",IF(B26&gt;=B30,ROUND(B30/B26,1),IF(B26+B27&gt;=B30,ROUND(1+(B30-B26)/B27,1),IF(B26+B27+B28&gt;=B30,ROUND(2+(B30-B26-B27)/B28,1),"Over 3 years")))),"")</f>
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="25" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="7">
       <c r="A7" s="28" t="inlineStr">
         <is>
-          <t>Loan (bank or lender)</t>
+          <t>Loan requested — bank or SBA 7(a) (amortized below)</t>
         </is>
       </c>
       <c r="B7" s="40">
@@ -9073,7 +9073,7 @@
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>SBA-guaranteed loan (7(a), through your bank)</t>
+          <t>Other loan (not in the schedule or the DSCR — enter your loan in row 7)</t>
         </is>
       </c>
       <c r="B8" s="49" t="n">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>The SBA backs the loan and your bank makes it. Check the current SBA 7(a) terms at sba.gov</t>
+          <t>A source of funds only: NOT amortized, so it is not in the schedule, the P&amp;L interest or the DSCR. Enter your bank or SBA 7(a) loan in row 7 ("Loan requested" in "0. Assumptions"); use this row only for a second loan</t>
         </is>
       </c>
       <c r="D8" s="28" t="n"/>
@@ -9093,7 +9093,7 @@
     <row r="9">
       <c r="A9" s="28" t="inlineStr">
         <is>
-          <t>SBA Microloan (nonprofit intermediaries, up to $50,000)</t>
+          <t>SBA Microloan (not in the schedule or the DSCR — enter your loan in row 7)</t>
         </is>
       </c>
       <c r="B9" s="49" t="n">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>Small loans made through nonprofit intermediaries; terms vary by lender</t>
+          <t>SBA Microloans go up to $50,000 through nonprofit intermediaries. Like row 8, a source of funds only: not in the schedule or the DSCR. If it is your only loan, enter it in row 7 instead</t>
         </is>
       </c>
       <c r="D9" s="28" t="n"/>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>Copy it into "Loan requested" in the "0. Assumptions" tab and the difference goes to zero</t>
+          <t>Copy it into "Loan requested" in the "0. Assumptions" tab and the difference goes to zero. Rows 8-11 lower this figure, but only the row-7 loan is amortized and counted in the DSCR</t>
         </is>
       </c>
       <c r="D18" s="28" t="n"/>
@@ -9474,11 +9474,11 @@
       </c>
       <c r="G27" s="61">
         <f>IFERROR(IF(E27="","",'3-Year P&amp;L'!$B$41-'3-Year P&amp;L'!$B$46+'3-Year P&amp;L'!$B$36+'3-Year P&amp;L'!$B$37),"")</f>
-        <v>46502.90914285716</v>
+        <v>45192.509142857154</v>
       </c>
       <c r="H27" s="61">
         <f>IFERROR(IF(OR(E27="",E27=0),"",G27/E27),"")</f>
-        <v>2.021389624540631</v>
+        <v>1.9644291243736232</v>
       </c>
     </row>
     <row r="28">
@@ -9507,11 +9507,11 @@
       </c>
       <c r="G28" s="61">
         <f>IFERROR(IF(E28="","",'3-Year P&amp;L'!$C$41-'3-Year P&amp;L'!$C$46+'3-Year P&amp;L'!$C$36+'3-Year P&amp;L'!$C$37),"")</f>
-        <v>60983.92154369548</v>
+        <v>59476.961543695455</v>
       </c>
       <c r="H28" s="61">
         <f>IFERROR(IF(OR(E28="",E28=0),"",G28/E28),"")</f>
-        <v>2.6508506358931845</v>
+        <v>2.585346060701125</v>
       </c>
     </row>
     <row r="29">
@@ -9540,11 +9540,11 @@
       </c>
       <c r="G29" s="61">
         <f>IFERROR(IF(E29="","",'3-Year P&amp;L'!$D$41-'3-Year P&amp;L'!$D$46+'3-Year P&amp;L'!$D$36+'3-Year P&amp;L'!$D$37),"")</f>
-        <v>70937.65258461765</v>
+        <v>69279.99658461765</v>
       </c>
       <c r="H29" s="61">
         <f>IFERROR(IF(OR(E29="",E29=0),"",G29/E29),"")</f>
-        <v>3.0835196671956826</v>
+        <v>3.0114646344844185</v>
       </c>
     </row>
     <row r="30">
@@ -9573,11 +9573,11 @@
       </c>
       <c r="G30" s="61">
         <f>IFERROR(IF(E30="","",'3-Year P&amp;L'!$D$41-'3-Year P&amp;L'!$D$46+'3-Year P&amp;L'!$D$36+'3-Year P&amp;L'!$D$37),"")</f>
-        <v>70937.65258461765</v>
+        <v>69279.99658461765</v>
       </c>
       <c r="H30" s="61">
         <f>IFERROR(IF(OR(E30="",E30=0),"",G30/E30),"")</f>
-        <v>3.0835196671956826</v>
+        <v>3.0114646344844185</v>
       </c>
     </row>
     <row r="31">
@@ -9606,11 +9606,11 @@
       </c>
       <c r="G31" s="61">
         <f>IFERROR(IF(E31="","",'3-Year P&amp;L'!$D$41-'3-Year P&amp;L'!$D$46+'3-Year P&amp;L'!$D$36+'3-Year P&amp;L'!$D$37),"")</f>
-        <v>70937.65258461765</v>
+        <v>69279.99658461765</v>
       </c>
       <c r="H31" s="61">
         <f>IFERROR(IF(OR(E31="",E31=0),"",G31/E31),"")</f>
-        <v>3.0835196671956826</v>
+        <v>3.0114646344844185</v>
       </c>
     </row>
     <row r="32">
@@ -9639,11 +9639,11 @@
       </c>
       <c r="G32" s="61">
         <f>IFERROR(IF(E32="","",'3-Year P&amp;L'!$D$41-'3-Year P&amp;L'!$D$46+'3-Year P&amp;L'!$D$36+'3-Year P&amp;L'!$D$37),"")</f>
-        <v>70937.65258461765</v>
+        <v>69279.99658461765</v>
       </c>
       <c r="H32" s="61">
         <f>IFERROR(IF(OR(E32="",E32=0),"",G32/E32),"")</f>
-        <v>3.0835196671956826</v>
+        <v>3.0114646344844185</v>
       </c>
     </row>
     <row r="33">
@@ -9672,11 +9672,11 @@
       </c>
       <c r="G33" s="61">
         <f>IFERROR(IF(E33="","",'3-Year P&amp;L'!$D$41-'3-Year P&amp;L'!$D$46+'3-Year P&amp;L'!$D$36+'3-Year P&amp;L'!$D$37),"")</f>
-        <v>70937.65258461765</v>
+        <v>69279.99658461765</v>
       </c>
       <c r="H33" s="61">
         <f>IFERROR(IF(OR(E33="",E33=0),"",G33/E33),"")</f>
-        <v>3.0835196671956826</v>
+        <v>3.0114646344844185</v>
       </c>
     </row>
     <row r="34">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="B51" s="61">
         <f>IFERROR(('3-Year P&amp;L'!$B$41-'3-Year P&amp;L'!$B$46+'3-Year P&amp;L'!$B$36+B44)/(B44+B45),"")</f>
-        <v>2.021389624540631</v>
+        <v>1.9644291243736232</v>
       </c>
       <c r="C51" s="28" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="B52" s="61">
         <f>IFERROR(('3-Year P&amp;L'!$C$41-'3-Year P&amp;L'!$C$46+'3-Year P&amp;L'!$C$36+B46)/(B46+B47),"")</f>
-        <v>2.6508506358931845</v>
+        <v>2.585346060701125</v>
       </c>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="28" t="n"/>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="B53" s="61">
         <f>IFERROR(('3-Year P&amp;L'!$D$41-'3-Year P&amp;L'!$D$46+'3-Year P&amp;L'!$D$36+B48)/(B48+B49),"")</f>
-        <v>3.0835196671956826</v>
+        <v>3.0114646344844185</v>
       </c>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="28" t="n"/>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B54" s="62">
         <f>IFERROR(IF(COUNT(H27:H41)=0,"",MIN(H27:H41)),"")</f>
-        <v>2.021389624540631</v>
+        <v>1.9644291243736232</v>
       </c>
       <c r="C54" s="25" t="inlineStr">
         <is>

--- a/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
+++ b/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
@@ -2113,7 +2113,7 @@
         <v>0.039071251755474073</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (used truck, build-out and wrap, propane and fire suppression, water tanks and handwashing sinks, plan review and drawings), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (used truck, build-out and wrap, propane and fire suppression, water tanks and handwashing sinks, plan review and drawings), not of the whole block: the other items are left out. No lender funds a "&amp;"build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 8% of the BUILD-OUT items of this block (used truck, build-out and wrap, propane and fire suppression, water tanks and handwashing sinks, plan review and drawings), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
+++ b/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
@@ -1560,7 +1560,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
@@ -8239,7 +8239,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>

--- a/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
+++ b/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
@@ -1560,7 +1560,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
         <v>0.039071251755474073</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (used truck, build-out and wrap, propane and fire suppression, water tanks and handwashing sinks, plan review and drawings), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (used truck, build-out and wrap, propane and fire suppression, water tanks and handwashing sinks, plan review and drawings), not of the whole block: the other items are left out. No lender funds a "&amp;"build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 8% of the BUILD-OUT items of this block (used truck, build-out and wrap, propane and fire suppression, water tanks and handwashing sinks, plan review and drawings), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>

--- a/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
+++ b/astro-site/public/dl/food-truck-business-plan/food-truck-financial-projections.xlsx
@@ -8236,7 +8236,7 @@
       <c r="N33" s="28" t="n"/>
       <c r="O33" s="28" t="n"/>
     </row>
-    <row r="34" ht="134.75" customHeight="1">
+    <row r="34" ht="149.5" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
           <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
